--- a/event_planner_forms/014_universal_miss_judge_information_form--event_planner_forms.xlsx
+++ b/event_planner_forms/014_universal_miss_judge_information_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -784,8 +784,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -813,12 +813,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'pageant_director',_'value':_1}</t>
+          <t>pageant_director</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Pageant Director', 'value': 1}</t>
+          <t>Pageant Director</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'judge',_'value':_2}</t>
+          <t>judge</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Judge', 'value': 2}</t>
+          <t>Judge</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'emcee',_'value':_3}</t>
+          <t>emcee</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Emcee', 'value': 3}</t>
+          <t>Emcee</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'beauty',_'value':_1}</t>
+          <t>beauty</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Beauty', 'value': 1}</t>
+          <t>Beauty</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'talent',_'value':_2}</t>
+          <t>talent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Talent', 'value': 2}</t>
+          <t>Talent</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'evening_wear',_'value':_3}</t>
+          <t>evening_wear</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Evening Wear', 'value': 3}</t>
+          <t>Evening Wear</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'swimsuits',_'value':_4}</t>
+          <t>swimsuits</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Swimsuits', 'value': 4}</t>
+          <t>Swimsuits</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'interview',_'value':_5}</t>
+          <t>interview</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Interview', 'value': 5}</t>
+          <t>Interview</t>
         </is>
       </c>
     </row>
